--- a/artfynd/A 46397-2025 artfynd.xlsx
+++ b/artfynd/A 46397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129663078</v>
       </c>
       <c r="B2" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129663077</v>
       </c>
       <c r="B4" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129663079</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 46397-2025 artfynd.xlsx
+++ b/artfynd/A 46397-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129663077</v>
+        <v>129663079</v>
       </c>
       <c r="B4" t="n">
-        <v>92863</v>
+        <v>79070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546828</v>
+        <v>546921</v>
       </c>
       <c r="R4" t="n">
-        <v>6736467</v>
+        <v>6736543</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -959,39 +959,39 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jakob Wallin</t>
+          <t>Jakob Wallin, Andreas Öster</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129663079</v>
+        <v>129663077</v>
       </c>
       <c r="B5" t="n">
-        <v>79070</v>
+        <v>92863</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546921</v>
+        <v>546828</v>
       </c>
       <c r="R5" t="n">
-        <v>6736543</v>
+        <v>6736467</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jakob Wallin, Andreas Öster</t>
+          <t>Jakob Wallin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 46397-2025 artfynd.xlsx
+++ b/artfynd/A 46397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129663078</v>
       </c>
       <c r="B2" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129663079</v>
+        <v>129663077</v>
       </c>
       <c r="B4" t="n">
-        <v>79070</v>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546921</v>
+        <v>546828</v>
       </c>
       <c r="R4" t="n">
-        <v>6736543</v>
+        <v>6736467</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -959,39 +959,39 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jakob Wallin, Andreas Öster</t>
+          <t>Jakob Wallin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129663077</v>
+        <v>129663079</v>
       </c>
       <c r="B5" t="n">
-        <v>92863</v>
+        <v>79075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546828</v>
+        <v>546921</v>
       </c>
       <c r="R5" t="n">
-        <v>6736467</v>
+        <v>6736543</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jakob Wallin</t>
+          <t>Jakob Wallin, Andreas Öster</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 46397-2025 artfynd.xlsx
+++ b/artfynd/A 46397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129663078</v>
       </c>
       <c r="B2" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129663077</v>
       </c>
       <c r="B4" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129663079</v>
       </c>
       <c r="B5" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 46397-2025 artfynd.xlsx
+++ b/artfynd/A 46397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129663078</v>
       </c>
       <c r="B2" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129663077</v>
       </c>
       <c r="B4" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129663079</v>
       </c>
       <c r="B5" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 46397-2025 artfynd.xlsx
+++ b/artfynd/A 46397-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129663077</v>
+        <v>129663079</v>
       </c>
       <c r="B4" t="n">
-        <v>92875</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546828</v>
+        <v>546921</v>
       </c>
       <c r="R4" t="n">
-        <v>6736467</v>
+        <v>6736543</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -959,39 +959,39 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jakob Wallin</t>
+          <t>Jakob Wallin, Andreas Öster</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129663079</v>
+        <v>129663077</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>92875</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546921</v>
+        <v>546828</v>
       </c>
       <c r="R5" t="n">
-        <v>6736543</v>
+        <v>6736467</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jakob Wallin, Andreas Öster</t>
+          <t>Jakob Wallin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 46397-2025 artfynd.xlsx
+++ b/artfynd/A 46397-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129663079</v>
+        <v>129663077</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>92875</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546921</v>
+        <v>546828</v>
       </c>
       <c r="R4" t="n">
-        <v>6736543</v>
+        <v>6736467</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -959,39 +959,39 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jakob Wallin, Andreas Öster</t>
+          <t>Jakob Wallin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129663077</v>
+        <v>129663079</v>
       </c>
       <c r="B5" t="n">
-        <v>92875</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546828</v>
+        <v>546921</v>
       </c>
       <c r="R5" t="n">
-        <v>6736467</v>
+        <v>6736543</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jakob Wallin</t>
+          <t>Jakob Wallin, Andreas Öster</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 46397-2025 artfynd.xlsx
+++ b/artfynd/A 46397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129663078</v>
       </c>
       <c r="B2" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129663077</v>
       </c>
       <c r="B4" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46397-2025 artfynd.xlsx
+++ b/artfynd/A 46397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129663078</v>
       </c>
       <c r="B2" t="n">
-        <v>92917</v>
+        <v>92919</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129663077</v>
       </c>
       <c r="B4" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46397-2025 artfynd.xlsx
+++ b/artfynd/A 46397-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129663077</v>
+        <v>129663079</v>
       </c>
       <c r="B4" t="n">
-        <v>92881</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546828</v>
+        <v>546921</v>
       </c>
       <c r="R4" t="n">
-        <v>6736467</v>
+        <v>6736543</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -959,39 +959,39 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jakob Wallin</t>
+          <t>Jakob Wallin, Andreas Öster</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129663079</v>
+        <v>129663077</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>92881</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546921</v>
+        <v>546828</v>
       </c>
       <c r="R5" t="n">
-        <v>6736543</v>
+        <v>6736467</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jakob Wallin, Andreas Öster</t>
+          <t>Jakob Wallin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 46397-2025 artfynd.xlsx
+++ b/artfynd/A 46397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129663078</v>
       </c>
       <c r="B2" t="n">
-        <v>92919</v>
+        <v>92922</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129663079</v>
+        <v>129663077</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>92884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546921</v>
+        <v>546828</v>
       </c>
       <c r="R4" t="n">
-        <v>6736543</v>
+        <v>6736467</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -959,39 +959,39 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jakob Wallin, Andreas Öster</t>
+          <t>Jakob Wallin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129663077</v>
+        <v>129663079</v>
       </c>
       <c r="B5" t="n">
-        <v>92881</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546828</v>
+        <v>546921</v>
       </c>
       <c r="R5" t="n">
-        <v>6736467</v>
+        <v>6736543</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jakob Wallin</t>
+          <t>Jakob Wallin, Andreas Öster</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 46397-2025 artfynd.xlsx
+++ b/artfynd/A 46397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129663078</v>
       </c>
       <c r="B2" t="n">
-        <v>92922</v>
+        <v>92925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129663076</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129663077</v>
       </c>
       <c r="B4" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129663079</v>
       </c>
       <c r="B5" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 46397-2025 artfynd.xlsx
+++ b/artfynd/A 46397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129663078</v>
       </c>
       <c r="B2" t="n">
-        <v>92925</v>
+        <v>92926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129663077</v>
       </c>
       <c r="B4" t="n">
-        <v>92887</v>
+        <v>92888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129663079</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
